--- a/data/latest/voterreg_congressional.xlsx
+++ b/data/latest/voterreg_congressional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/ayake_pa_gov/Documents/Documents/0   WEEKLY     0 VR Stats November/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pagov-my.sharepoint.com/personal/wcharpenti_pa_gov/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F23E7D6-AB8E-465E-9A23-E5CFA471570E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{86D6DCE3-B1CF-4A58-B1FD-D8A142CF1257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D09C5D02-EE89-439C-99A4-DA43C4C11C78}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="747">
   <si>
     <t>DistrictCode</t>
   </si>
@@ -55,49 +55,49 @@
     <t>BUCKS</t>
   </si>
   <si>
-    <t>194503</t>
-  </si>
-  <si>
-    <t>201723</t>
-  </si>
-  <si>
-    <t>2680</t>
+    <t>194682</t>
+  </si>
+  <si>
+    <t>201808</t>
+  </si>
+  <si>
+    <t>2681</t>
   </si>
   <si>
     <t>613</t>
   </si>
   <si>
-    <t>71136</t>
-  </si>
-  <si>
-    <t>14935</t>
-  </si>
-  <si>
-    <t>485590</t>
+    <t>71270</t>
+  </si>
+  <si>
+    <t>14926</t>
+  </si>
+  <si>
+    <t>485980</t>
   </si>
   <si>
     <t>MONTGOMERY</t>
   </si>
   <si>
-    <t>34423</t>
-  </si>
-  <si>
-    <t>36330</t>
+    <t>34466</t>
+  </si>
+  <si>
+    <t>36340</t>
   </si>
   <si>
     <t>491</t>
   </si>
   <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>12308</t>
-  </si>
-  <si>
-    <t>3242</t>
-  </si>
-  <si>
-    <t>86902</t>
+    <t>107</t>
+  </si>
+  <si>
+    <t>12332</t>
+  </si>
+  <si>
+    <t>3245</t>
+  </si>
+  <si>
+    <t>86981</t>
   </si>
   <si>
     <t/>
@@ -106,25 +106,25 @@
     <t>Sub Total</t>
   </si>
   <si>
-    <t>228926</t>
-  </si>
-  <si>
-    <t>238053</t>
-  </si>
-  <si>
-    <t>3171</t>
-  </si>
-  <si>
-    <t>721</t>
-  </si>
-  <si>
-    <t>83444</t>
-  </si>
-  <si>
-    <t>18177</t>
-  </si>
-  <si>
-    <t>572492</t>
+    <t>229148</t>
+  </si>
+  <si>
+    <t>238148</t>
+  </si>
+  <si>
+    <t>3172</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>83602</t>
+  </si>
+  <si>
+    <t>18171</t>
+  </si>
+  <si>
+    <t>572961</t>
   </si>
   <si>
     <t>2</t>
@@ -133,49 +133,49 @@
     <t>PHILADELPHIA</t>
   </si>
   <si>
-    <t>295673</t>
-  </si>
-  <si>
-    <t>80600</t>
-  </si>
-  <si>
-    <t>1954</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>72384</t>
-  </si>
-  <si>
-    <t>8620</t>
-  </si>
-  <si>
-    <t>460371</t>
+    <t>296009</t>
+  </si>
+  <si>
+    <t>80653</t>
+  </si>
+  <si>
+    <t>1965</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>72598</t>
+  </si>
+  <si>
+    <t>8614</t>
+  </si>
+  <si>
+    <t>460987</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>453534</t>
-  </si>
-  <si>
-    <t>43239</t>
-  </si>
-  <si>
-    <t>2235</t>
-  </si>
-  <si>
-    <t>1663</t>
-  </si>
-  <si>
-    <t>77686</t>
-  </si>
-  <si>
-    <t>9585</t>
-  </si>
-  <si>
-    <t>587942</t>
+    <t>454107</t>
+  </si>
+  <si>
+    <t>43274</t>
+  </si>
+  <si>
+    <t>2250</t>
+  </si>
+  <si>
+    <t>1690</t>
+  </si>
+  <si>
+    <t>77932</t>
+  </si>
+  <si>
+    <t>9589</t>
+  </si>
+  <si>
+    <t>588842</t>
   </si>
   <si>
     <t>4</t>
@@ -184,67 +184,67 @@
     <t>BERKS</t>
   </si>
   <si>
-    <t>33009</t>
-  </si>
-  <si>
-    <t>46345</t>
+    <t>33036</t>
+  </si>
+  <si>
+    <t>46356</t>
   </si>
   <si>
     <t>641</t>
   </si>
   <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>13139</t>
-  </si>
-  <si>
-    <t>2777</t>
-  </si>
-  <si>
-    <t>96052</t>
-  </si>
-  <si>
-    <t>226651</t>
-  </si>
-  <si>
-    <t>155218</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>626</t>
-  </si>
-  <si>
-    <t>62092</t>
-  </si>
-  <si>
-    <t>16146</t>
-  </si>
-  <si>
-    <t>463036</t>
-  </si>
-  <si>
-    <t>259660</t>
-  </si>
-  <si>
-    <t>201563</t>
-  </si>
-  <si>
-    <t>2944</t>
+    <t>140</t>
+  </si>
+  <si>
+    <t>13169</t>
+  </si>
+  <si>
+    <t>2784</t>
+  </si>
+  <si>
+    <t>96126</t>
+  </si>
+  <si>
+    <t>226943</t>
+  </si>
+  <si>
+    <t>155232</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>62199</t>
+  </si>
+  <si>
+    <t>16133</t>
+  </si>
+  <si>
+    <t>463441</t>
+  </si>
+  <si>
+    <t>259979</t>
+  </si>
+  <si>
+    <t>201588</t>
+  </si>
+  <si>
+    <t>2948</t>
   </si>
   <si>
     <t>767</t>
   </si>
   <si>
-    <t>75231</t>
-  </si>
-  <si>
-    <t>18923</t>
-  </si>
-  <si>
-    <t>559088</t>
+    <t>75368</t>
+  </si>
+  <si>
+    <t>18917</t>
+  </si>
+  <si>
+    <t>559567</t>
   </si>
   <si>
     <t>5</t>
@@ -259,151 +259,154 @@
     <t>DELAWARE</t>
   </si>
   <si>
-    <t>203683</t>
-  </si>
-  <si>
-    <t>142582</t>
-  </si>
-  <si>
-    <t>1681</t>
-  </si>
-  <si>
-    <t>592</t>
-  </si>
-  <si>
-    <t>49998</t>
-  </si>
-  <si>
-    <t>13359</t>
-  </si>
-  <si>
-    <t>411895</t>
-  </si>
-  <si>
-    <t>45315</t>
-  </si>
-  <si>
-    <t>16013</t>
-  </si>
-  <si>
-    <t>349</t>
+    <t>204018</t>
+  </si>
+  <si>
+    <t>142558</t>
+  </si>
+  <si>
+    <t>1687</t>
+  </si>
+  <si>
+    <t>598</t>
+  </si>
+  <si>
+    <t>50123</t>
+  </si>
+  <si>
+    <t>13355</t>
+  </si>
+  <si>
+    <t>412339</t>
+  </si>
+  <si>
+    <t>45369</t>
+  </si>
+  <si>
+    <t>16017</t>
+  </si>
+  <si>
+    <t>347</t>
   </si>
   <si>
     <t>109</t>
   </si>
   <si>
-    <t>11154</t>
-  </si>
-  <si>
-    <t>2432</t>
-  </si>
-  <si>
-    <t>75372</t>
-  </si>
-  <si>
-    <t>33045</t>
-  </si>
-  <si>
-    <t>7491</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>5804</t>
-  </si>
-  <si>
-    <t>961</t>
-  </si>
-  <si>
-    <t>47572</t>
-  </si>
-  <si>
-    <t>282043</t>
-  </si>
-  <si>
-    <t>166086</t>
-  </si>
-  <si>
-    <t>2171</t>
-  </si>
-  <si>
-    <t>831</t>
-  </si>
-  <si>
-    <t>66956</t>
-  </si>
-  <si>
-    <t>16752</t>
-  </si>
-  <si>
-    <t>534839</t>
+    <t>11187</t>
+  </si>
+  <si>
+    <t>2434</t>
+  </si>
+  <si>
+    <t>75463</t>
+  </si>
+  <si>
+    <t>33033</t>
+  </si>
+  <si>
+    <t>7502</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>5825</t>
+  </si>
+  <si>
+    <t>965</t>
+  </si>
+  <si>
+    <t>47596</t>
+  </si>
+  <si>
+    <t>282420</t>
+  </si>
+  <si>
+    <t>166077</t>
+  </si>
+  <si>
+    <t>2176</t>
+  </si>
+  <si>
+    <t>836</t>
+  </si>
+  <si>
+    <t>67135</t>
+  </si>
+  <si>
+    <t>16754</t>
+  </si>
+  <si>
+    <t>535398</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>60691</t>
-  </si>
-  <si>
-    <t>49249</t>
-  </si>
-  <si>
-    <t>842</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>24271</t>
-  </si>
-  <si>
-    <t>4211</t>
-  </si>
-  <si>
-    <t>139534</t>
-  </si>
-  <si>
-    <t>161850</t>
-  </si>
-  <si>
-    <t>151799</t>
-  </si>
-  <si>
-    <t>2081</t>
-  </si>
-  <si>
-    <t>488</t>
-  </si>
-  <si>
-    <t>59366</t>
-  </si>
-  <si>
-    <t>15244</t>
-  </si>
-  <si>
-    <t>390828</t>
-  </si>
-  <si>
-    <t>222541</t>
-  </si>
-  <si>
-    <t>201048</t>
-  </si>
-  <si>
-    <t>2923</t>
-  </si>
-  <si>
-    <t>758</t>
-  </si>
-  <si>
-    <t>83637</t>
-  </si>
-  <si>
-    <t>19455</t>
-  </si>
-  <si>
-    <t>530362</t>
+    <t>60720</t>
+  </si>
+  <si>
+    <t>49282</t>
+  </si>
+  <si>
+    <t>845</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>24306</t>
+  </si>
+  <si>
+    <t>4207</t>
+  </si>
+  <si>
+    <t>139631</t>
+  </si>
+  <si>
+    <t>162056</t>
+  </si>
+  <si>
+    <t>151747</t>
+  </si>
+  <si>
+    <t>2085</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>59476</t>
+  </si>
+  <si>
+    <t>15218</t>
+  </si>
+  <si>
+    <t>391068</t>
+  </si>
+  <si>
+    <t>222776</t>
+  </si>
+  <si>
+    <t>201029</t>
+  </si>
+  <si>
+    <t>2930</t>
+  </si>
+  <si>
+    <t>757</t>
+  </si>
+  <si>
+    <t>83782</t>
+  </si>
+  <si>
+    <t>19425</t>
+  </si>
+  <si>
+    <t>530699</t>
   </si>
   <si>
     <t>7</t>
@@ -412,1093 +415,1102 @@
     <t>CARBON</t>
   </si>
   <si>
-    <t>14078</t>
-  </si>
-  <si>
-    <t>23940</t>
+    <t>14088</t>
+  </si>
+  <si>
+    <t>23951</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>5909</t>
+  </si>
+  <si>
+    <t>1547</t>
+  </si>
+  <si>
+    <t>45834</t>
+  </si>
+  <si>
+    <t>LEHIGH</t>
+  </si>
+  <si>
+    <t>112300</t>
+  </si>
+  <si>
+    <t>89521</t>
+  </si>
+  <si>
+    <t>1392</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>46009</t>
+  </si>
+  <si>
+    <t>5541</t>
+  </si>
+  <si>
+    <t>255167</t>
+  </si>
+  <si>
+    <t>MONROE</t>
+  </si>
+  <si>
+    <t>2695</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1432</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>9555</t>
+  </si>
+  <si>
+    <t>NORTHAMPTON</t>
+  </si>
+  <si>
+    <t>96755</t>
+  </si>
+  <si>
+    <t>87001</t>
+  </si>
+  <si>
+    <t>1396</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>40170</t>
+  </si>
+  <si>
+    <t>7817</t>
+  </si>
+  <si>
+    <t>233460</t>
+  </si>
+  <si>
+    <t>225838</t>
+  </si>
+  <si>
+    <t>205473</t>
+  </si>
+  <si>
+    <t>3157</t>
+  </si>
+  <si>
+    <t>789</t>
+  </si>
+  <si>
+    <t>93520</t>
+  </si>
+  <si>
+    <t>15239</t>
+  </si>
+  <si>
+    <t>544016</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>LACKAWANNA</t>
+  </si>
+  <si>
+    <t>77044</t>
+  </si>
+  <si>
+    <t>52322</t>
+  </si>
+  <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>17479</t>
+  </si>
+  <si>
+    <t>2590</t>
+  </si>
+  <si>
+    <t>150355</t>
+  </si>
+  <si>
+    <t>LUZERNE</t>
+  </si>
+  <si>
+    <t>78186</t>
+  </si>
+  <si>
+    <t>72494</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>22995</t>
+  </si>
+  <si>
+    <t>3749</t>
+  </si>
+  <si>
+    <t>178702</t>
+  </si>
+  <si>
+    <t>46219</t>
+  </si>
+  <si>
+    <t>38419</t>
+  </si>
+  <si>
+    <t>664</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>19510</t>
+  </si>
+  <si>
+    <t>3720</t>
+  </si>
+  <si>
+    <t>108696</t>
+  </si>
+  <si>
+    <t>PIKE</t>
+  </si>
+  <si>
+    <t>13678</t>
+  </si>
+  <si>
+    <t>23145</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>8568</t>
+  </si>
+  <si>
+    <t>1790</t>
+  </si>
+  <si>
+    <t>47528</t>
+  </si>
+  <si>
+    <t>WAYNE</t>
+  </si>
+  <si>
+    <t>8747</t>
+  </si>
+  <si>
+    <t>21758</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>5230</t>
+  </si>
+  <si>
+    <t>797</t>
+  </si>
+  <si>
+    <t>36794</t>
+  </si>
+  <si>
+    <t>223874</t>
+  </si>
+  <si>
+    <t>208138</t>
+  </si>
+  <si>
+    <t>2845</t>
+  </si>
+  <si>
+    <t>790</t>
+  </si>
+  <si>
+    <t>73782</t>
+  </si>
+  <si>
+    <t>12646</t>
+  </si>
+  <si>
+    <t>522075</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10718</t>
+  </si>
+  <si>
+    <t>22411</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>4595</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>39190</t>
+  </si>
+  <si>
+    <t>BRADFORD</t>
+  </si>
+  <si>
+    <t>7838</t>
+  </si>
+  <si>
+    <t>25683</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>3939</t>
+  </si>
+  <si>
+    <t>1228</t>
+  </si>
+  <si>
+    <t>38991</t>
+  </si>
+  <si>
+    <t>COLUMBIA</t>
+  </si>
+  <si>
+    <t>11811</t>
+  </si>
+  <si>
+    <t>22448</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>4900</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>40650</t>
+  </si>
+  <si>
+    <t>FAYETTE</t>
+  </si>
+  <si>
+    <t>LEBANON</t>
+  </si>
+  <si>
+    <t>25610</t>
+  </si>
+  <si>
+    <t>52685</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>12476</t>
+  </si>
+  <si>
+    <t>3020</t>
+  </si>
+  <si>
+    <t>94460</t>
+  </si>
+  <si>
+    <t>7839</t>
+  </si>
+  <si>
+    <t>18292</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>3049</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>29860</t>
+  </si>
+  <si>
+    <t>LYCOMING</t>
+  </si>
+  <si>
+    <t>12821</t>
+  </si>
+  <si>
+    <t>25674</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>5393</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>45637</t>
+  </si>
+  <si>
+    <t>MONTOUR</t>
+  </si>
+  <si>
+    <t>3779</t>
+  </si>
+  <si>
+    <t>6567</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>12387</t>
+  </si>
+  <si>
+    <t>NORTHUMBERLAND</t>
+  </si>
+  <si>
+    <t>15348</t>
+  </si>
+  <si>
+    <t>31963</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>5886</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>55434</t>
+  </si>
+  <si>
+    <t>SCHUYLKILL</t>
+  </si>
+  <si>
+    <t>25433</t>
+  </si>
+  <si>
+    <t>53199</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>10277</t>
+  </si>
+  <si>
+    <t>3063</t>
+  </si>
+  <si>
+    <t>92659</t>
+  </si>
+  <si>
+    <t>SULLIVAN</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>2859</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>4472</t>
+  </si>
+  <si>
+    <t>SUSQUEHANNA</t>
+  </si>
+  <si>
+    <t>6146</t>
+  </si>
+  <si>
+    <t>17289</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>2903</t>
+  </si>
+  <si>
+    <t>929</t>
+  </si>
+  <si>
+    <t>27463</t>
+  </si>
+  <si>
+    <t>WYOMING</t>
+  </si>
+  <si>
+    <t>4731</t>
+  </si>
+  <si>
+    <t>11296</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1843</t>
+  </si>
+  <si>
+    <t>18531</t>
+  </si>
+  <si>
+    <t>133143</t>
+  </si>
+  <si>
+    <t>290366</t>
+  </si>
+  <si>
+    <t>2953</t>
+  </si>
+  <si>
+    <t>669</t>
+  </si>
+  <si>
+    <t>57275</t>
+  </si>
+  <si>
+    <t>15328</t>
+  </si>
+  <si>
+    <t>499734</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>CUMBERLAND</t>
+  </si>
+  <si>
+    <t>58422</t>
+  </si>
+  <si>
+    <t>79324</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>25420</t>
+  </si>
+  <si>
+    <t>4670</t>
+  </si>
+  <si>
+    <t>169150</t>
+  </si>
+  <si>
+    <t>DAUPHIN</t>
+  </si>
+  <si>
+    <t>87120</t>
+  </si>
+  <si>
+    <t>75924</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>31826</t>
+  </si>
+  <si>
+    <t>5709</t>
+  </si>
+  <si>
+    <t>202102</t>
+  </si>
+  <si>
+    <t>YORK</t>
+  </si>
+  <si>
+    <t>57278</t>
+  </si>
+  <si>
+    <t>79810</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>30285</t>
+  </si>
+  <si>
+    <t>3409</t>
+  </si>
+  <si>
+    <t>172193</t>
+  </si>
+  <si>
+    <t>202820</t>
+  </si>
+  <si>
+    <t>235058</t>
+  </si>
+  <si>
+    <t>3345</t>
+  </si>
+  <si>
+    <t>903</t>
+  </si>
+  <si>
+    <t>87531</t>
+  </si>
+  <si>
+    <t>13788</t>
+  </si>
+  <si>
+    <t>543445</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>LANCASTER</t>
+  </si>
+  <si>
+    <t>113781</t>
+  </si>
+  <si>
+    <t>183764</t>
+  </si>
+  <si>
+    <t>2248</t>
+  </si>
+  <si>
+    <t>572</t>
+  </si>
+  <si>
+    <t>52046</t>
+  </si>
+  <si>
+    <t>13223</t>
+  </si>
+  <si>
+    <t>365634</t>
+  </si>
+  <si>
+    <t>39824</t>
+  </si>
+  <si>
+    <t>88650</t>
+  </si>
+  <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>24288</t>
+  </si>
+  <si>
+    <t>2734</t>
+  </si>
+  <si>
+    <t>156865</t>
+  </si>
+  <si>
+    <t>153605</t>
+  </si>
+  <si>
+    <t>272414</t>
+  </si>
+  <si>
+    <t>3423</t>
+  </si>
+  <si>
+    <t>766</t>
+  </si>
+  <si>
+    <t>76334</t>
+  </si>
+  <si>
+    <t>15957</t>
+  </si>
+  <si>
+    <t>522499</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>ALLEGHENY</t>
+  </si>
+  <si>
+    <t>286723</t>
+  </si>
+  <si>
+    <t>112638</t>
+  </si>
+  <si>
+    <t>2487</t>
+  </si>
+  <si>
+    <t>1402</t>
+  </si>
+  <si>
+    <t>61436</t>
+  </si>
+  <si>
+    <t>15002</t>
+  </si>
+  <si>
+    <t>479688</t>
+  </si>
+  <si>
+    <t>WESTMORELAND</t>
+  </si>
+  <si>
+    <t>27766</t>
+  </si>
+  <si>
+    <t>43370</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>7926</t>
+  </si>
+  <si>
+    <t>2478</t>
+  </si>
+  <si>
+    <t>82079</t>
+  </si>
+  <si>
+    <t>314489</t>
+  </si>
+  <si>
+    <t>156008</t>
+  </si>
+  <si>
+    <t>2957</t>
+  </si>
+  <si>
+    <t>1471</t>
+  </si>
+  <si>
+    <t>69362</t>
+  </si>
+  <si>
+    <t>17480</t>
+  </si>
+  <si>
+    <t>561767</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>19258</t>
+  </si>
+  <si>
+    <t>44075</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>10814</t>
+  </si>
+  <si>
+    <t>2168</t>
+  </si>
+  <si>
+    <t>76918</t>
+  </si>
+  <si>
+    <t>BEDFORD</t>
+  </si>
+  <si>
+    <t>5260</t>
+  </si>
+  <si>
+    <t>24579</t>
+  </si>
+  <si>
+    <t>2332</t>
+  </si>
+  <si>
+    <t>741</t>
+  </si>
+  <si>
+    <t>33060</t>
+  </si>
+  <si>
+    <t>BLAIR</t>
+  </si>
+  <si>
+    <t>19842</t>
+  </si>
+  <si>
+    <t>50596</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>8528</t>
+  </si>
+  <si>
+    <t>2190</t>
+  </si>
+  <si>
+    <t>81665</t>
+  </si>
+  <si>
+    <t>CAMBRIA</t>
+  </si>
+  <si>
+    <t>29378</t>
+  </si>
+  <si>
+    <t>46501</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>7973</t>
+  </si>
+  <si>
+    <t>1646</t>
+  </si>
+  <si>
+    <t>85982</t>
+  </si>
+  <si>
+    <t>3750</t>
+  </si>
+  <si>
+    <t>8916</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>15394</t>
+  </si>
+  <si>
+    <t>FRANKLIN</t>
+  </si>
+  <si>
+    <t>23629</t>
+  </si>
+  <si>
+    <t>64351</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>14273</t>
+  </si>
+  <si>
+    <t>2661</t>
+  </si>
+  <si>
+    <t>105672</t>
+  </si>
+  <si>
+    <t>FULTON</t>
+  </si>
+  <si>
+    <t>1473</t>
+  </si>
+  <si>
+    <t>7472</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>921</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>10130</t>
+  </si>
+  <si>
+    <t>HUNTINGDON</t>
+  </si>
+  <si>
+    <t>6025</t>
+  </si>
+  <si>
+    <t>18878</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>2391</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>27894</t>
+  </si>
+  <si>
+    <t>JUNIATA</t>
+  </si>
+  <si>
+    <t>2544</t>
+  </si>
+  <si>
+    <t>10031</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>14095</t>
+  </si>
+  <si>
+    <t>MIFFLIN</t>
+  </si>
+  <si>
+    <t>5404</t>
+  </si>
+  <si>
+    <t>18648</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>2527</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>27199</t>
+  </si>
+  <si>
+    <t>PERRY</t>
+  </si>
+  <si>
+    <t>6038</t>
+  </si>
+  <si>
+    <t>20943</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>3476</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>31314</t>
+  </si>
+  <si>
+    <t>SOMERSET</t>
   </si>
   <si>
     <t>286</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>5902</t>
-  </si>
-  <si>
-    <t>1547</t>
-  </si>
-  <si>
-    <t>45804</t>
-  </si>
-  <si>
-    <t>LEHIGH</t>
-  </si>
-  <si>
-    <t>112171</t>
-  </si>
-  <si>
-    <t>89468</t>
-  </si>
-  <si>
-    <t>1394</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>45948</t>
-  </si>
-  <si>
-    <t>5545</t>
-  </si>
-  <si>
-    <t>254925</t>
-  </si>
-  <si>
-    <t>MONROE</t>
-  </si>
-  <si>
-    <t>2689</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>1429</t>
-  </si>
-  <si>
-    <t>335</t>
-  </si>
-  <si>
-    <t>9546</t>
-  </si>
-  <si>
-    <t>NORTHAMPTON</t>
-  </si>
-  <si>
-    <t>96596</t>
-  </si>
-  <si>
-    <t>86979</t>
-  </si>
-  <si>
-    <t>1397</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>40109</t>
-  </si>
-  <si>
-    <t>7818</t>
-  </si>
-  <si>
-    <t>233219</t>
-  </si>
-  <si>
-    <t>225534</t>
-  </si>
-  <si>
-    <t>205387</t>
-  </si>
-  <si>
-    <t>3157</t>
-  </si>
-  <si>
-    <t>783</t>
-  </si>
-  <si>
-    <t>93388</t>
-  </si>
-  <si>
-    <t>15245</t>
-  </si>
-  <si>
-    <t>543494</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>LACKAWANNA</t>
-  </si>
-  <si>
-    <t>76952</t>
-  </si>
-  <si>
-    <t>52297</t>
-  </si>
-  <si>
-    <t>696</t>
-  </si>
-  <si>
-    <t>222</t>
-  </si>
-  <si>
-    <t>17428</t>
-  </si>
-  <si>
-    <t>2592</t>
-  </si>
-  <si>
-    <t>150187</t>
-  </si>
-  <si>
-    <t>LUZERNE</t>
-  </si>
-  <si>
-    <t>77991</t>
-  </si>
-  <si>
-    <t>72497</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>22950</t>
-  </si>
-  <si>
-    <t>3754</t>
-  </si>
-  <si>
-    <t>178461</t>
-  </si>
-  <si>
-    <t>46132</t>
-  </si>
-  <si>
-    <t>38396</t>
-  </si>
-  <si>
-    <t>662</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>19452</t>
-  </si>
-  <si>
-    <t>3726</t>
-  </si>
-  <si>
-    <t>108530</t>
-  </si>
-  <si>
-    <t>PIKE</t>
-  </si>
-  <si>
-    <t>13661</t>
-  </si>
-  <si>
-    <t>23136</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>8555</t>
-  </si>
-  <si>
-    <t>1792</t>
-  </si>
-  <si>
-    <t>47492</t>
-  </si>
-  <si>
-    <t>WAYNE</t>
-  </si>
-  <si>
-    <t>8727</t>
-  </si>
-  <si>
-    <t>21749</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>5226</t>
-  </si>
-  <si>
-    <t>796</t>
-  </si>
-  <si>
-    <t>36759</t>
-  </si>
-  <si>
-    <t>223463</t>
-  </si>
-  <si>
-    <t>208075</t>
-  </si>
-  <si>
-    <t>2839</t>
-  </si>
-  <si>
-    <t>781</t>
-  </si>
-  <si>
-    <t>73611</t>
-  </si>
-  <si>
-    <t>12660</t>
-  </si>
-  <si>
-    <t>521429</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10710</t>
-  </si>
-  <si>
-    <t>22401</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>4589</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>39162</t>
-  </si>
-  <si>
-    <t>BRADFORD</t>
-  </si>
-  <si>
-    <t>7833</t>
-  </si>
-  <si>
-    <t>25655</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>3931</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>38950</t>
-  </si>
-  <si>
-    <t>COLUMBIA</t>
-  </si>
-  <si>
-    <t>11809</t>
-  </si>
-  <si>
-    <t>22445</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>4893</t>
-  </si>
-  <si>
-    <t>1187</t>
-  </si>
-  <si>
-    <t>40638</t>
-  </si>
-  <si>
-    <t>FAYETTE</t>
-  </si>
-  <si>
-    <t>LEBANON</t>
-  </si>
-  <si>
-    <t>25573</t>
-  </si>
-  <si>
-    <t>52678</t>
-  </si>
-  <si>
-    <t>553</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>12452</t>
-  </si>
-  <si>
-    <t>3020</t>
-  </si>
-  <si>
-    <t>94390</t>
-  </si>
-  <si>
-    <t>7835</t>
-  </si>
-  <si>
-    <t>18291</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>3046</t>
-  </si>
-  <si>
-    <t>513</t>
-  </si>
-  <si>
-    <t>29852</t>
-  </si>
-  <si>
-    <t>LYCOMING</t>
-  </si>
-  <si>
-    <t>12803</t>
-  </si>
-  <si>
-    <t>25672</t>
-  </si>
-  <si>
-    <t>276</t>
+    <t>718</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>122887</t>
+  </si>
+  <si>
+    <t>315708</t>
+  </si>
+  <si>
+    <t>2742</t>
+  </si>
+  <si>
+    <t>585</t>
+  </si>
+  <si>
+    <t>56702</t>
+  </si>
+  <si>
+    <t>11797</t>
+  </si>
+  <si>
+    <t>510421</t>
+  </si>
+  <si>
+    <t>29447</t>
+  </si>
+  <si>
+    <t>41335</t>
+  </si>
+  <si>
+    <t>355</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>5375</t>
-  </si>
-  <si>
-    <t>1414</t>
-  </si>
-  <si>
-    <t>45598</t>
-  </si>
-  <si>
-    <t>MONTOUR</t>
-  </si>
-  <si>
-    <t>3776</t>
-  </si>
-  <si>
-    <t>6567</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>1626</t>
-  </si>
-  <si>
-    <t>333</t>
-  </si>
-  <si>
-    <t>12382</t>
-  </si>
-  <si>
-    <t>NORTHUMBERLAND</t>
-  </si>
-  <si>
-    <t>15348</t>
-  </si>
-  <si>
-    <t>31953</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>5873</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>55413</t>
-  </si>
-  <si>
-    <t>SCHUYLKILL</t>
-  </si>
-  <si>
-    <t>25412</t>
-  </si>
-  <si>
-    <t>53186</t>
-  </si>
-  <si>
-    <t>561</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>10259</t>
-  </si>
-  <si>
-    <t>3067</t>
-  </si>
-  <si>
-    <t>92610</t>
-  </si>
-  <si>
-    <t>SULLIVAN</t>
-  </si>
-  <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>2857</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>4466</t>
-  </si>
-  <si>
-    <t>SUSQUEHANNA</t>
-  </si>
-  <si>
-    <t>6140</t>
-  </si>
-  <si>
-    <t>17284</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>2898</t>
-  </si>
-  <si>
-    <t>928</t>
-  </si>
-  <si>
-    <t>27445</t>
-  </si>
-  <si>
-    <t>WYOMING</t>
-  </si>
-  <si>
-    <t>4723</t>
-  </si>
-  <si>
-    <t>11305</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>1835</t>
-  </si>
-  <si>
-    <t>559</t>
-  </si>
-  <si>
-    <t>18521</t>
-  </si>
-  <si>
-    <t>133031</t>
-  </si>
-  <si>
-    <t>290294</t>
-  </si>
-  <si>
-    <t>2948</t>
-  </si>
-  <si>
-    <t>665</t>
-  </si>
-  <si>
-    <t>57159</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>499427</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>CUMBERLAND</t>
-  </si>
-  <si>
-    <t>58287</t>
-  </si>
-  <si>
-    <t>79296</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>25378</t>
-  </si>
-  <si>
-    <t>4675</t>
-  </si>
-  <si>
-    <t>168949</t>
-  </si>
-  <si>
-    <t>DAUPHIN</t>
-  </si>
-  <si>
-    <t>87008</t>
-  </si>
-  <si>
-    <t>75909</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>31729</t>
-  </si>
-  <si>
-    <t>5711</t>
-  </si>
-  <si>
-    <t>201881</t>
-  </si>
-  <si>
-    <t>YORK</t>
-  </si>
-  <si>
-    <t>57193</t>
-  </si>
-  <si>
-    <t>79749</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>30232</t>
-  </si>
-  <si>
-    <t>3402</t>
-  </si>
-  <si>
-    <t>171982</t>
-  </si>
-  <si>
-    <t>202488</t>
-  </si>
-  <si>
-    <t>234954</t>
-  </si>
-  <si>
-    <t>3339</t>
-  </si>
-  <si>
-    <t>904</t>
-  </si>
-  <si>
-    <t>87339</t>
-  </si>
-  <si>
-    <t>13788</t>
-  </si>
-  <si>
-    <t>542812</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>LANCASTER</t>
-  </si>
-  <si>
-    <t>113638</t>
-  </si>
-  <si>
-    <t>183738</t>
-  </si>
-  <si>
-    <t>2249</t>
-  </si>
-  <si>
-    <t>574</t>
-  </si>
-  <si>
-    <t>51995</t>
-  </si>
-  <si>
-    <t>13226</t>
-  </si>
-  <si>
-    <t>365420</t>
-  </si>
-  <si>
-    <t>39764</t>
-  </si>
-  <si>
-    <t>88634</t>
-  </si>
-  <si>
-    <t>1175</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>24249</t>
-  </si>
-  <si>
-    <t>2737</t>
-  </si>
-  <si>
-    <t>156754</t>
-  </si>
-  <si>
-    <t>153402</t>
-  </si>
-  <si>
-    <t>272372</t>
-  </si>
-  <si>
-    <t>3424</t>
-  </si>
-  <si>
-    <t>769</t>
-  </si>
-  <si>
-    <t>76244</t>
-  </si>
-  <si>
-    <t>15963</t>
-  </si>
-  <si>
-    <t>522174</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>ALLEGHENY</t>
-  </si>
-  <si>
-    <t>286296</t>
-  </si>
-  <si>
-    <t>112630</t>
-  </si>
-  <si>
-    <t>2484</t>
-  </si>
-  <si>
-    <t>1396</t>
-  </si>
-  <si>
-    <t>61238</t>
-  </si>
-  <si>
-    <t>15027</t>
-  </si>
-  <si>
-    <t>479071</t>
-  </si>
-  <si>
-    <t>WESTMORELAND</t>
-  </si>
-  <si>
-    <t>27730</t>
-  </si>
-  <si>
-    <t>43354</t>
-  </si>
-  <si>
-    <t>470</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>7907</t>
-  </si>
-  <si>
-    <t>2479</t>
-  </si>
-  <si>
-    <t>82009</t>
-  </si>
-  <si>
-    <t>314026</t>
-  </si>
-  <si>
-    <t>155984</t>
-  </si>
-  <si>
-    <t>2954</t>
-  </si>
-  <si>
-    <t>1465</t>
-  </si>
-  <si>
-    <t>69145</t>
-  </si>
-  <si>
-    <t>17506</t>
-  </si>
-  <si>
-    <t>561080</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>19238</t>
-  </si>
-  <si>
-    <t>44051</t>
-  </si>
-  <si>
-    <t>501</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>10810</t>
-  </si>
-  <si>
-    <t>2168</t>
-  </si>
-  <si>
-    <t>76870</t>
-  </si>
-  <si>
-    <t>BEDFORD</t>
-  </si>
-  <si>
-    <t>5253</t>
-  </si>
-  <si>
-    <t>24587</t>
-  </si>
-  <si>
-    <t>2328</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>33059</t>
-  </si>
-  <si>
-    <t>BLAIR</t>
-  </si>
-  <si>
-    <t>19829</t>
-  </si>
-  <si>
-    <t>50567</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>8520</t>
-  </si>
-  <si>
-    <t>2191</t>
-  </si>
-  <si>
-    <t>81616</t>
-  </si>
-  <si>
-    <t>CAMBRIA</t>
-  </si>
-  <si>
-    <t>29366</t>
-  </si>
-  <si>
-    <t>46488</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>7950</t>
-  </si>
-  <si>
-    <t>1648</t>
-  </si>
-  <si>
-    <t>85935</t>
-  </si>
-  <si>
-    <t>3736</t>
-  </si>
-  <si>
-    <t>8912</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2196</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>15367</t>
-  </si>
-  <si>
-    <t>FRANKLIN</t>
-  </si>
-  <si>
-    <t>23589</t>
-  </si>
-  <si>
-    <t>64309</t>
-  </si>
-  <si>
-    <t>625</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>14260</t>
-  </si>
-  <si>
-    <t>2664</t>
-  </si>
-  <si>
-    <t>105580</t>
-  </si>
-  <si>
-    <t>FULTON</t>
-  </si>
-  <si>
-    <t>1471</t>
-  </si>
-  <si>
-    <t>7475</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>10130</t>
-  </si>
-  <si>
-    <t>HUNTINGDON</t>
-  </si>
-  <si>
-    <t>6020</t>
-  </si>
-  <si>
-    <t>18884</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2391</t>
-  </si>
-  <si>
-    <t>452</t>
-  </si>
-  <si>
-    <t>27895</t>
-  </si>
-  <si>
-    <t>JUNIATA</t>
-  </si>
-  <si>
-    <t>2542</t>
-  </si>
-  <si>
-    <t>10024</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>14081</t>
-  </si>
-  <si>
-    <t>MIFFLIN</t>
-  </si>
-  <si>
-    <t>5389</t>
-  </si>
-  <si>
-    <t>18635</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>2518</t>
-  </si>
-  <si>
-    <t>472</t>
-  </si>
-  <si>
-    <t>27162</t>
-  </si>
-  <si>
-    <t>PERRY</t>
-  </si>
-  <si>
-    <t>6028</t>
-  </si>
-  <si>
-    <t>20939</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>3468</t>
-  </si>
-  <si>
-    <t>607</t>
-  </si>
-  <si>
-    <t>31294</t>
-  </si>
-  <si>
-    <t>SOMERSET</t>
-  </si>
-  <si>
-    <t>718</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>122747</t>
-  </si>
-  <si>
-    <t>315589</t>
-  </si>
-  <si>
-    <t>2745</t>
-  </si>
-  <si>
-    <t>581</t>
-  </si>
-  <si>
-    <t>56620</t>
-  </si>
-  <si>
-    <t>11805</t>
-  </si>
-  <si>
-    <t>510087</t>
-  </si>
-  <si>
-    <t>29439</t>
-  </si>
-  <si>
-    <t>41321</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>6746</t>
+    <t>6756</t>
   </si>
   <si>
     <t>1652</t>
   </si>
   <si>
-    <t>79570</t>
+    <t>79603</t>
   </si>
   <si>
     <t>GREENE</t>
   </si>
   <si>
-    <t>7334</t>
-  </si>
-  <si>
-    <t>12197</t>
+    <t>7336</t>
+  </si>
+  <si>
+    <t>12205</t>
   </si>
   <si>
     <t>87</t>
@@ -1513,76 +1525,76 @@
     <t>484</t>
   </si>
   <si>
-    <t>21809</t>
+    <t>21819</t>
   </si>
   <si>
     <t>INDIANA</t>
   </si>
   <si>
-    <t>13075</t>
-  </si>
-  <si>
-    <t>25493</t>
+    <t>13089</t>
+  </si>
+  <si>
+    <t>25504</t>
   </si>
   <si>
     <t>253</t>
   </si>
   <si>
-    <t>4402</t>
+    <t>4405</t>
   </si>
   <si>
     <t>1249</t>
   </si>
   <si>
-    <t>44521</t>
-  </si>
-  <si>
-    <t>10209</t>
-  </si>
-  <si>
-    <t>32090</t>
+    <t>44549</t>
+  </si>
+  <si>
+    <t>10207</t>
+  </si>
+  <si>
+    <t>32076</t>
   </si>
   <si>
     <t>239</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>4366</t>
   </si>
   <si>
     <t>480</t>
   </si>
   <si>
-    <t>47423</t>
+    <t>47407</t>
   </si>
   <si>
     <t>WASHINGTON</t>
   </si>
   <si>
-    <t>52637</t>
-  </si>
-  <si>
-    <t>72759</t>
-  </si>
-  <si>
-    <t>747</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>16051</t>
-  </si>
-  <si>
-    <t>145221</t>
-  </si>
-  <si>
-    <t>59111</t>
-  </si>
-  <si>
-    <t>87445</t>
+    <t>52683</t>
+  </si>
+  <si>
+    <t>72809</t>
+  </si>
+  <si>
+    <t>746</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>16072</t>
+  </si>
+  <si>
+    <t>2900</t>
+  </si>
+  <si>
+    <t>145338</t>
+  </si>
+  <si>
+    <t>59165</t>
+  </si>
+  <si>
+    <t>87484</t>
   </si>
   <si>
     <t>901</t>
@@ -1591,43 +1603,40 @@
     <t>183</t>
   </si>
   <si>
-    <t>16201</t>
-  </si>
-  <si>
-    <t>5081</t>
-  </si>
-  <si>
-    <t>168922</t>
-  </si>
-  <si>
-    <t>171805</t>
-  </si>
-  <si>
-    <t>271305</t>
+    <t>16224</t>
+  </si>
+  <si>
+    <t>5083</t>
+  </si>
+  <si>
+    <t>169040</t>
+  </si>
+  <si>
+    <t>171927</t>
+  </si>
+  <si>
+    <t>271413</t>
   </si>
   <si>
     <t>2581</t>
   </si>
   <si>
-    <t>492</t>
-  </si>
-  <si>
-    <t>49439</t>
-  </si>
-  <si>
-    <t>11844</t>
-  </si>
-  <si>
-    <t>507466</t>
+    <t>49496</t>
+  </si>
+  <si>
+    <t>11848</t>
+  </si>
+  <si>
+    <t>507756</t>
   </si>
   <si>
     <t>ARMSTRONG</t>
   </si>
   <si>
-    <t>10630</t>
-  </si>
-  <si>
-    <t>27683</t>
+    <t>10631</t>
+  </si>
+  <si>
+    <t>27700</t>
   </si>
   <si>
     <t>258</t>
@@ -1636,19 +1645,19 @@
     <t>47</t>
   </si>
   <si>
-    <t>3740</t>
-  </si>
-  <si>
-    <t>1282</t>
-  </si>
-  <si>
-    <t>43640</t>
+    <t>3743</t>
+  </si>
+  <si>
+    <t>1279</t>
+  </si>
+  <si>
+    <t>43658</t>
   </si>
   <si>
     <t>CAMERON</t>
   </si>
   <si>
-    <t>661</t>
+    <t>663</t>
   </si>
   <si>
     <t>1841</t>
@@ -1657,352 +1666,343 @@
     <t>256</t>
   </si>
   <si>
-    <t>2881</t>
+    <t>2883</t>
   </si>
   <si>
     <t>CENTRE</t>
   </si>
   <si>
-    <t>41578</t>
-  </si>
-  <si>
-    <t>41784</t>
-  </si>
-  <si>
-    <t>573</t>
+    <t>41656</t>
+  </si>
+  <si>
+    <t>41812</t>
+  </si>
+  <si>
+    <t>576</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>16221</t>
+  </si>
+  <si>
+    <t>1958</t>
+  </si>
+  <si>
+    <t>102384</t>
+  </si>
+  <si>
+    <t>CLARION</t>
+  </si>
+  <si>
+    <t>5047</t>
+  </si>
+  <si>
+    <t>15496</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>2086</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>23270</t>
+  </si>
+  <si>
+    <t>CLEARFIELD</t>
+  </si>
+  <si>
+    <t>12051</t>
+  </si>
+  <si>
+    <t>31454</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>4339</t>
+  </si>
+  <si>
+    <t>1461</t>
+  </si>
+  <si>
+    <t>49630</t>
+  </si>
+  <si>
+    <t>CLINTON</t>
+  </si>
+  <si>
+    <t>6107</t>
+  </si>
+  <si>
+    <t>13275</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2455</t>
+  </si>
+  <si>
+    <t>596</t>
+  </si>
+  <si>
+    <t>22579</t>
+  </si>
+  <si>
+    <t>ELK</t>
+  </si>
+  <si>
+    <t>5769</t>
+  </si>
+  <si>
+    <t>12126</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>1791</t>
+  </si>
+  <si>
+    <t>20461</t>
+  </si>
+  <si>
+    <t>FOREST</t>
+  </si>
+  <si>
+    <t>2069</t>
+  </si>
+  <si>
+    <t>3268</t>
+  </si>
+  <si>
+    <t>791</t>
+  </si>
+  <si>
+    <t>3373</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>4613</t>
+  </si>
+  <si>
+    <t>JEFFERSON</t>
+  </si>
+  <si>
+    <t>5455</t>
+  </si>
+  <si>
+    <t>19481</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>2322</t>
+  </si>
+  <si>
+    <t>754</t>
+  </si>
+  <si>
+    <t>28193</t>
+  </si>
+  <si>
+    <t>5444</t>
+  </si>
+  <si>
+    <t>18069</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>27172</t>
+  </si>
+  <si>
+    <t>McKEAN</t>
+  </si>
+  <si>
+    <t>5336</t>
+  </si>
+  <si>
+    <t>16205</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>16206</t>
-  </si>
-  <si>
-    <t>1959</t>
-  </si>
-  <si>
-    <t>102260</t>
-  </si>
-  <si>
-    <t>CLARION</t>
-  </si>
-  <si>
-    <t>5042</t>
-  </si>
-  <si>
-    <t>15507</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>2085</t>
-  </si>
-  <si>
-    <t>505</t>
-  </si>
-  <si>
-    <t>23275</t>
-  </si>
-  <si>
-    <t>CLEARFIELD</t>
-  </si>
-  <si>
-    <t>12035</t>
-  </si>
-  <si>
-    <t>31432</t>
-  </si>
-  <si>
-    <t>4331</t>
-  </si>
-  <si>
-    <t>1461</t>
-  </si>
-  <si>
-    <t>49587</t>
-  </si>
-  <si>
-    <t>CLINTON</t>
-  </si>
-  <si>
-    <t>6089</t>
-  </si>
-  <si>
-    <t>13270</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>2450</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>22553</t>
-  </si>
-  <si>
-    <t>ELK</t>
-  </si>
-  <si>
-    <t>5762</t>
-  </si>
-  <si>
-    <t>12122</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>1783</t>
-  </si>
-  <si>
-    <t>663</t>
-  </si>
-  <si>
-    <t>20443</t>
-  </si>
-  <si>
-    <t>FOREST</t>
-  </si>
-  <si>
-    <t>789</t>
-  </si>
-  <si>
-    <t>2065</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>3262</t>
-  </si>
-  <si>
-    <t>788</t>
-  </si>
-  <si>
-    <t>3372</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>4607</t>
-  </si>
-  <si>
-    <t>JEFFERSON</t>
-  </si>
-  <si>
-    <t>5451</t>
-  </si>
-  <si>
-    <t>19465</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>2316</t>
-  </si>
-  <si>
-    <t>756</t>
-  </si>
-  <si>
-    <t>28168</t>
-  </si>
-  <si>
-    <t>5448</t>
-  </si>
-  <si>
-    <t>18065</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>2692</t>
-  </si>
-  <si>
-    <t>27167</t>
-  </si>
-  <si>
-    <t>McKEAN</t>
-  </si>
-  <si>
-    <t>5315</t>
-  </si>
-  <si>
-    <t>16212</t>
-  </si>
-  <si>
-    <t>161</t>
+    <t>2767</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
+    <t>25336</t>
+  </si>
+  <si>
+    <t>POTTER</t>
+  </si>
+  <si>
+    <t>1742</t>
+  </si>
+  <si>
+    <t>7999</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>11015</t>
+  </si>
+  <si>
+    <t>SNYDER</t>
+  </si>
+  <si>
+    <t>4937</t>
+  </si>
+  <si>
+    <t>15964</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2390</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>23964</t>
+  </si>
+  <si>
+    <t>TIOGA</t>
+  </si>
+  <si>
+    <t>4938</t>
+  </si>
+  <si>
+    <t>18117</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>3004</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>26853</t>
+  </si>
+  <si>
+    <t>UNION</t>
+  </si>
+  <si>
+    <t>7902</t>
+  </si>
+  <si>
+    <t>14357</t>
+  </si>
+  <si>
+    <t>121</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>2757</t>
-  </si>
-  <si>
-    <t>830</t>
-  </si>
-  <si>
-    <t>25311</t>
-  </si>
-  <si>
-    <t>POTTER</t>
-  </si>
-  <si>
-    <t>1740</t>
-  </si>
-  <si>
-    <t>7986</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>10996</t>
-  </si>
-  <si>
-    <t>SNYDER</t>
-  </si>
-  <si>
-    <t>4927</t>
-  </si>
-  <si>
-    <t>15957</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2386</t>
-  </si>
-  <si>
-    <t>498</t>
-  </si>
-  <si>
-    <t>23944</t>
-  </si>
-  <si>
-    <t>TIOGA</t>
-  </si>
-  <si>
-    <t>4938</t>
-  </si>
-  <si>
-    <t>18107</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>2992</t>
-  </si>
-  <si>
-    <t>602</t>
-  </si>
-  <si>
-    <t>26832</t>
-  </si>
-  <si>
-    <t>UNION</t>
-  </si>
-  <si>
-    <t>7896</t>
-  </si>
-  <si>
-    <t>14367</t>
-  </si>
-  <si>
-    <t>3277</t>
-  </si>
-  <si>
-    <t>821</t>
-  </si>
-  <si>
-    <t>26519</t>
+    <t>3279</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>26518</t>
   </si>
   <si>
     <t>VENANGO</t>
   </si>
   <si>
-    <t>4754</t>
-  </si>
-  <si>
-    <t>12499</t>
+    <t>4757</t>
+  </si>
+  <si>
+    <t>12506</t>
   </si>
   <si>
     <t>139</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>2130</t>
-  </si>
-  <si>
-    <t>596</t>
-  </si>
-  <si>
-    <t>20138</t>
+    <t>2136</t>
+  </si>
+  <si>
+    <t>597</t>
+  </si>
+  <si>
+    <t>20156</t>
   </si>
   <si>
     <t>WARREN</t>
   </si>
   <si>
-    <t>6352</t>
-  </si>
-  <si>
-    <t>15225</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>2610</t>
+    <t>6353</t>
+  </si>
+  <si>
+    <t>15234</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>2619</t>
   </si>
   <si>
     <t>1085</t>
   </si>
   <si>
-    <t>25434</t>
-  </si>
-  <si>
-    <t>130195</t>
-  </si>
-  <si>
-    <t>286959</t>
-  </si>
-  <si>
-    <t>572</t>
-  </si>
-  <si>
-    <t>53602</t>
-  </si>
-  <si>
-    <t>12997</t>
-  </si>
-  <si>
-    <t>487017</t>
+    <t>25454</t>
+  </si>
+  <si>
+    <t>130368</t>
+  </si>
+  <si>
+    <t>287078</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>53702</t>
+  </si>
+  <si>
+    <t>12987</t>
+  </si>
+  <si>
+    <t>487407</t>
   </si>
   <si>
     <t>16</t>
@@ -2011,244 +2011,256 @@
     <t>BUTLER</t>
   </si>
   <si>
-    <t>39364</t>
-  </si>
-  <si>
-    <t>83007</t>
-  </si>
-  <si>
-    <t>891</t>
-  </si>
-  <si>
-    <t>16472</t>
-  </si>
-  <si>
-    <t>4112</t>
-  </si>
-  <si>
-    <t>143981</t>
+    <t>39431</t>
+  </si>
+  <si>
+    <t>83043</t>
+  </si>
+  <si>
+    <t>887</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>16510</t>
+  </si>
+  <si>
+    <t>4113</t>
+  </si>
+  <si>
+    <t>144118</t>
   </si>
   <si>
     <t>CRAWFORD</t>
   </si>
   <si>
-    <t>14420</t>
+    <t>14440</t>
   </si>
   <si>
     <t>31791</t>
   </si>
   <si>
-    <t>267</t>
+    <t>266</t>
   </si>
   <si>
     <t>61</t>
   </si>
   <si>
-    <t>4971</t>
-  </si>
-  <si>
-    <t>1506</t>
-  </si>
-  <si>
-    <t>53016</t>
+    <t>4970</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>53032</t>
   </si>
   <si>
     <t>ERIE</t>
   </si>
   <si>
-    <t>76530</t>
-  </si>
-  <si>
-    <t>70796</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>20932</t>
-  </si>
-  <si>
-    <t>5347</t>
-  </si>
-  <si>
-    <t>174910</t>
+    <t>76554</t>
+  </si>
+  <si>
+    <t>70779</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>20940</t>
+  </si>
+  <si>
+    <t>5345</t>
+  </si>
+  <si>
+    <t>174921</t>
   </si>
   <si>
     <t>LAWRENCE</t>
   </si>
   <si>
-    <t>19664</t>
-  </si>
-  <si>
-    <t>30112</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>5676</t>
-  </si>
-  <si>
-    <t>1573</t>
-  </si>
-  <si>
-    <t>57337</t>
+    <t>19681</t>
+  </si>
+  <si>
+    <t>30104</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>5677</t>
+  </si>
+  <si>
+    <t>1575</t>
+  </si>
+  <si>
+    <t>57349</t>
   </si>
   <si>
     <t>MERCER</t>
   </si>
   <si>
-    <t>23160</t>
-  </si>
-  <si>
-    <t>38309</t>
-  </si>
-  <si>
-    <t>390</t>
+    <t>23192</t>
+  </si>
+  <si>
+    <t>38330</t>
+  </si>
+  <si>
+    <t>392</t>
   </si>
   <si>
     <t>85</t>
   </si>
   <si>
-    <t>8468</t>
-  </si>
-  <si>
-    <t>1555</t>
-  </si>
-  <si>
-    <t>71967</t>
-  </si>
-  <si>
-    <t>7644</t>
+    <t>8474</t>
+  </si>
+  <si>
+    <t>1554</t>
+  </si>
+  <si>
+    <t>72027</t>
+  </si>
+  <si>
+    <t>3282</t>
+  </si>
+  <si>
+    <t>7656</t>
   </si>
   <si>
     <t>76</t>
   </si>
   <si>
-    <t>1337</t>
+    <t>1344</t>
   </si>
   <si>
     <t>375</t>
   </si>
   <si>
-    <t>12721</t>
-  </si>
-  <si>
-    <t>176415</t>
-  </si>
-  <si>
-    <t>261659</t>
-  </si>
-  <si>
-    <t>2893</t>
-  </si>
-  <si>
-    <t>57856</t>
-  </si>
-  <si>
-    <t>14468</t>
-  </si>
-  <si>
-    <t>513932</t>
+    <t>12747</t>
+  </si>
+  <si>
+    <t>176580</t>
+  </si>
+  <si>
+    <t>261703</t>
+  </si>
+  <si>
+    <t>2887</t>
+  </si>
+  <si>
+    <t>643</t>
+  </si>
+  <si>
+    <t>57915</t>
+  </si>
+  <si>
+    <t>14466</t>
+  </si>
+  <si>
+    <t>514194</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>218838</t>
-  </si>
-  <si>
-    <t>150412</t>
-  </si>
-  <si>
-    <t>2393</t>
-  </si>
-  <si>
-    <t>732</t>
-  </si>
-  <si>
-    <t>54437</t>
-  </si>
-  <si>
-    <t>14576</t>
-  </si>
-  <si>
-    <t>441388</t>
+    <t>219062</t>
+  </si>
+  <si>
+    <t>150431</t>
+  </si>
+  <si>
+    <t>2397</t>
+  </si>
+  <si>
+    <t>736</t>
+  </si>
+  <si>
+    <t>54527</t>
+  </si>
+  <si>
+    <t>14571</t>
+  </si>
+  <si>
+    <t>441724</t>
   </si>
   <si>
     <t>BEAVER</t>
   </si>
   <si>
-    <t>45755</t>
-  </si>
-  <si>
-    <t>51886</t>
-  </si>
-  <si>
-    <t>652</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>11877</t>
-  </si>
-  <si>
-    <t>3928</t>
-  </si>
-  <si>
-    <t>114230</t>
-  </si>
-  <si>
-    <t>264593</t>
-  </si>
-  <si>
-    <t>202298</t>
-  </si>
-  <si>
-    <t>3045</t>
-  </si>
-  <si>
-    <t>864</t>
-  </si>
-  <si>
-    <t>66314</t>
-  </si>
-  <si>
-    <t>18504</t>
-  </si>
-  <si>
-    <t>555618</t>
+    <t>45771</t>
+  </si>
+  <si>
+    <t>51931</t>
+  </si>
+  <si>
+    <t>655</t>
+  </si>
+  <si>
+    <t>11895</t>
+  </si>
+  <si>
+    <t>3922</t>
+  </si>
+  <si>
+    <t>114308</t>
+  </si>
+  <si>
+    <t>264833</t>
+  </si>
+  <si>
+    <t>202362</t>
+  </si>
+  <si>
+    <t>3052</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>66422</t>
+  </si>
+  <si>
+    <t>18493</t>
+  </si>
+  <si>
+    <t>556032</t>
   </si>
   <si>
     <t>State Total</t>
   </si>
   <si>
-    <t>3860076</t>
-  </si>
-  <si>
-    <t>3635465</t>
-  </si>
-  <si>
-    <t>48015</t>
-  </si>
-  <si>
-    <t>14397</t>
-  </si>
-  <si>
-    <t>1200055</t>
-  </si>
-  <si>
-    <t>251622</t>
-  </si>
-  <si>
-    <t>9009630</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> *   There are no voters in this county for this district - it is an empty field.</t>
+    <t>3864803</t>
+  </si>
+  <si>
+    <t>3636490</t>
+  </si>
+  <si>
+    <t>48078</t>
+  </si>
+  <si>
+    <t>14472</t>
+  </si>
+  <si>
+    <t>1202458</t>
+  </si>
+  <si>
+    <t>251499</t>
+  </si>
+  <si>
+    <t>9017800</t>
+  </si>
+  <si>
+    <t>*There are no voters in this county for this district - it is an empty field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
   </si>
 </sst>
 </file>
@@ -2632,6 +2644,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2661,6 +2676,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -3097,7 +3115,7 @@
         <v>77</v>
       </c>
       <c r="J16" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -3172,19 +3190,19 @@
         <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -3195,25 +3213,25 @@
         <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -3247,60 +3265,60 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
         <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
         <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -3311,25 +3329,25 @@
         <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -3363,118 +3381,118 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -3485,25 +3503,25 @@
         <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -3537,147 +3555,147 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="G33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E34" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I34" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D35" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F35" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D36" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E36" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F36" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G36" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H36" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -3688,25 +3706,25 @@
         <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E37" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F37" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I37" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -3740,350 +3758,350 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F39" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H39" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C40" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D40" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F40" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G40" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B41" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H41" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I41" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F42" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G42" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I42" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C43" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D43" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E43" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F43" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G43" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I43" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C44" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D44" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E44" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F44" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H44" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I44" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C45" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D45" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E45" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F45" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G45" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H45" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I45" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C46" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D46" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E46" t="s">
-        <v>273</v>
+        <v>152</v>
       </c>
       <c r="F46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H47" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D48" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F48" t="s">
         <v>52</v>
       </c>
       <c r="G48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I48" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C49" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F49" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G49" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H49" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I49" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C50" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D50" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E50" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F50" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="G50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H50" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="I50" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -4094,25 +4112,25 @@
         <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -4146,22 +4164,22 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D53" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F53" t="s">
-        <v>320</v>
+        <v>133</v>
       </c>
       <c r="G53" t="s">
         <v>321</v>
@@ -4175,7 +4193,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B54" t="s">
         <v>324</v>
@@ -4190,45 +4208,45 @@
         <v>327</v>
       </c>
       <c r="F54" t="s">
-        <v>268</v>
+        <v>328</v>
       </c>
       <c r="G54" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H54" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I54" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C55" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D55" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E55" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F55" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G55" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I55" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -4239,25 +4257,25 @@
         <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D56" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E56" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G56" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I56" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -4291,60 +4309,60 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B58" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C58" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D58" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E58" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F58" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G58" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H58" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I58" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C59" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D59" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E59" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F59" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G59" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H59" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I59" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -4355,25 +4373,25 @@
         <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D60" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E60" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F60" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G60" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H60" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I60" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -4407,60 +4425,60 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C62" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D62" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E62" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F62" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G62" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H62" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I62" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B63" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C63" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D63" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E63" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F63" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G63" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H63" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I63" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -4471,25 +4489,25 @@
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D64" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E64" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F64" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G64" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H64" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I64" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -4523,335 +4541,335 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B66" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C66" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D66" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E66" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F66" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G66" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H66" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I66" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B67" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C67" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D67" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E67" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F67" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G67" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H67" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I67" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C68" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D68" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E68" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F68" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G68" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H68" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I68" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C69" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D69" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E69" t="s">
-        <v>141</v>
+        <v>419</v>
       </c>
       <c r="F69" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G69" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H69" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I69" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C70" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D70" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E70" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F70" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G70" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H70" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I70" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C71" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D71" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E71" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F71" t="s">
-        <v>433</v>
+        <v>292</v>
       </c>
       <c r="G71" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H71" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I71" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C72" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D72" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E72" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F72" t="s">
         <v>75</v>
       </c>
       <c r="G72" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H72" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I72" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C73" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D73" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E73" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F73" t="s">
-        <v>297</v>
+        <v>449</v>
       </c>
       <c r="G73" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H73" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I73" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C74" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D74" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E74" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F74" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G74" t="s">
-        <v>456</v>
+        <v>238</v>
       </c>
       <c r="H74" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I74" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B75" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C75" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D75" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E75" t="s">
-        <v>282</v>
+        <v>463</v>
       </c>
       <c r="F75" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G75" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H75" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I75" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C76" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D76" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E76" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F76" t="s">
-        <v>297</v>
+        <v>449</v>
       </c>
       <c r="G76" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H76" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I76" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C77" t="s">
-        <v>132</v>
+        <v>476</v>
       </c>
       <c r="D77" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E77" t="s">
         <v>52</v>
@@ -4860,13 +4878,13 @@
         <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="H77" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I77" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -4877,25 +4895,25 @@
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D78" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E78" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F78" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G78" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="H78" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="I78" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -4929,176 +4947,176 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C80" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D80" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E80" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F80" t="s">
-        <v>258</v>
+        <v>490</v>
       </c>
       <c r="G80" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="H80" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="I80" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B81" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C81" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D81" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E81" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F81" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G81" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H81" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="I81" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B82" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C82" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D82" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E82" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F82" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G82" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H82" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="I82" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B83" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C83" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D83" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E83" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F83" t="s">
-        <v>508</v>
+        <v>298</v>
       </c>
       <c r="G83" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="H83" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I83" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B84" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C84" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D84" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E84" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F84" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G84" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="H84" t="s">
-        <v>298</v>
+        <v>521</v>
       </c>
       <c r="I84" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C85" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D85" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E85" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F85" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G85" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H85" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="I85" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -5109,25 +5127,25 @@
         <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D86" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E86" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F86" t="s">
-        <v>529</v>
+        <v>21</v>
       </c>
       <c r="G86" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="H86" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="I86" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -5161,231 +5179,231 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B88" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C88" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D88" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E88" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F88" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G88" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H88" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I88" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B89" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C89" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D89" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E89" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F89" t="s">
         <v>44</v>
       </c>
       <c r="G89" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H89" t="s">
         <v>89</v>
       </c>
       <c r="I89" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B90" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C90" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D90" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E90" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F90" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G90" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H90" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I90" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B91" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C91" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D91" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E91" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F91" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G91" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H91" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="I91" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B92" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C92" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D92" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E92" t="s">
-        <v>335</v>
+        <v>567</v>
       </c>
       <c r="F92" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G92" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="H92" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I92" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B93" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C93" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D93" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E93" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F93" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G93" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H93" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="I93" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B94" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C94" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D94" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E94" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="F94" t="s">
-        <v>579</v>
+        <v>252</v>
       </c>
       <c r="G94" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H94" t="s">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="I94" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B95" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C95" t="s">
-        <v>584</v>
+        <v>165</v>
       </c>
       <c r="D95" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E95" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F95" t="s">
         <v>44</v>
       </c>
       <c r="G95" t="s">
-        <v>586</v>
+        <v>336</v>
       </c>
       <c r="H95" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I95" t="s">
         <v>587</v>
@@ -5393,10 +5411,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B96" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C96" t="s">
         <v>588</v>
@@ -5405,7 +5423,7 @@
         <v>589</v>
       </c>
       <c r="E96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F96" t="s">
         <v>9</v>
@@ -5422,7 +5440,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B97" t="s">
         <v>593</v>
@@ -5437,7 +5455,7 @@
         <v>596</v>
       </c>
       <c r="F97" t="s">
-        <v>579</v>
+        <v>306</v>
       </c>
       <c r="G97" t="s">
         <v>597</v>
@@ -5451,10 +5469,10 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B98" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C98" t="s">
         <v>600</v>
@@ -5466,181 +5484,181 @@
         <v>602</v>
       </c>
       <c r="F98" t="s">
-        <v>571</v>
+        <v>464</v>
       </c>
       <c r="G98" t="s">
+        <v>147</v>
+      </c>
+      <c r="H98" t="s">
+        <v>165</v>
+      </c>
+      <c r="I98" t="s">
         <v>603</v>
-      </c>
-      <c r="H98" t="s">
-        <v>588</v>
-      </c>
-      <c r="I98" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B99" t="s">
+        <v>604</v>
+      </c>
+      <c r="C99" t="s">
         <v>605</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>606</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>607</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
+        <v>449</v>
+      </c>
+      <c r="G99" t="s">
         <v>608</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" t="s">
         <v>609</v>
       </c>
-      <c r="G99" t="s">
+      <c r="I99" t="s">
         <v>610</v>
-      </c>
-      <c r="H99" t="s">
-        <v>611</v>
-      </c>
-      <c r="I99" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
+        <v>611</v>
+      </c>
+      <c r="C100" t="s">
+        <v>612</v>
+      </c>
+      <c r="D100" t="s">
         <v>613</v>
       </c>
-      <c r="C100" t="s">
+      <c r="E100" t="s">
+        <v>134</v>
+      </c>
+      <c r="F100" t="s">
+        <v>216</v>
+      </c>
+      <c r="G100" t="s">
         <v>614</v>
       </c>
-      <c r="D100" t="s">
+      <c r="H100" t="s">
         <v>615</v>
       </c>
-      <c r="E100" t="s">
-        <v>133</v>
-      </c>
-      <c r="F100" t="s">
-        <v>214</v>
-      </c>
-      <c r="G100" t="s">
-        <v>180</v>
-      </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>616</v>
-      </c>
-      <c r="I100" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B101" t="s">
+        <v>617</v>
+      </c>
+      <c r="C101" t="s">
         <v>618</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>619</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>620</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>621</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>622</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>623</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
         <v>624</v>
-      </c>
-      <c r="I101" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B102" t="s">
+        <v>625</v>
+      </c>
+      <c r="C102" t="s">
         <v>626</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>627</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>628</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>629</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>630</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>631</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>632</v>
-      </c>
-      <c r="I102" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B103" t="s">
+        <v>633</v>
+      </c>
+      <c r="C103" t="s">
         <v>634</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>635</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>636</v>
       </c>
-      <c r="E103" t="s">
-        <v>570</v>
-      </c>
       <c r="F103" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="G103" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H103" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I103" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B104" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C104" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D104" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E104" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F104" t="s">
-        <v>644</v>
+        <v>560</v>
       </c>
       <c r="G104" t="s">
         <v>645</v>
@@ -5654,7 +5672,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B105" t="s">
         <v>648</v>
@@ -5666,10 +5684,10 @@
         <v>650</v>
       </c>
       <c r="E105" t="s">
+        <v>283</v>
+      </c>
+      <c r="F105" t="s">
         <v>651</v>
-      </c>
-      <c r="F105" t="s">
-        <v>609</v>
       </c>
       <c r="G105" t="s">
         <v>652</v>
@@ -5695,7 +5713,7 @@
         <v>656</v>
       </c>
       <c r="E106" t="s">
-        <v>603</v>
+        <v>147</v>
       </c>
       <c r="F106" t="s">
         <v>657</v>
@@ -5756,16 +5774,16 @@
         <v>665</v>
       </c>
       <c r="F108" t="s">
-        <v>291</v>
+        <v>666</v>
       </c>
       <c r="G108" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H108" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I108" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -5773,28 +5791,28 @@
         <v>661</v>
       </c>
       <c r="B109" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C109" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D109" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E109" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F109" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G109" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H109" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I109" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -5802,28 +5820,28 @@
         <v>661</v>
       </c>
       <c r="B110" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C110" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D110" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E110" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F110" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G110" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H110" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I110" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -5831,28 +5849,28 @@
         <v>661</v>
       </c>
       <c r="B111" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C111" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D111" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E111" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="F111" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G111" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H111" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="I111" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -5860,28 +5878,28 @@
         <v>661</v>
       </c>
       <c r="B112" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C112" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D112" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E112" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F112" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G112" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H112" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I112" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -5889,28 +5907,28 @@
         <v>661</v>
       </c>
       <c r="B113" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C113" t="s">
-        <v>637</v>
+        <v>702</v>
       </c>
       <c r="D113" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E113" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F113" t="s">
-        <v>369</v>
+        <v>457</v>
       </c>
       <c r="G113" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="H113" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="I113" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -5921,25 +5939,25 @@
         <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D114" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E114" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="F114" t="s">
-        <v>56</v>
+        <v>711</v>
       </c>
       <c r="G114" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H114" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="I114" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -5973,60 +5991,60 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B116" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C116" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D116" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E116" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F116" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="G116" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="H116" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="I116" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B117" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C117" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D117" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E117" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="F117" t="s">
-        <v>723</v>
+        <v>666</v>
       </c>
       <c r="G117" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="H117" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I117" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -6037,25 +6055,25 @@
         <v>27</v>
       </c>
       <c r="C118" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D118" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="E118" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F118" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G118" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H118" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="I118" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -6092,28 +6110,28 @@
         <v>26</v>
       </c>
       <c r="B120" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C120" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D120" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E120" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F120" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G120" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="H120" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="I120" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>
